--- a/Results/Phase 2/Methanol/methanol eutrophication marine results.xlsx
+++ b/Results/Phase 2/Methanol/methanol eutrophication marine results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.000362487352478047</v>
+        <v>0.0003365669382541116</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003894929288608958</v>
+        <v>0.000382894726887145</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003604248879885168</v>
+        <v>0.0003334269710037844</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000373373312273946</v>
+        <v>0.0003631692842039039</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003423471375520586</v>
+        <v>0.0003226475950740446</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003565522645375531</v>
+        <v>0.0003325606463839779</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003546413847725667</v>
+        <v>0.0003294876856344216</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003727388404657333</v>
+        <v>0.0003403854474087466</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003589033305822763</v>
+        <v>0.000333395456971169</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0004156984431714215</v>
+        <v>0.0003658284228728107</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000364204749295213</v>
+        <v>0.000336527920051307</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0004962895946904429</v>
+        <v>0.0004119429080267107</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003834266082016319</v>
+        <v>0.0003474215641845497</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0007114517597838843</v>
+        <v>0.0006882464511748154</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003462803726930713</v>
+        <v>0.0003264799275624146</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003367299764746061</v>
+        <v>0.0003198355714674275</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003426305884503226</v>
+        <v>0.0003228007612563904</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003546097557710894</v>
+        <v>0.000331336193846069</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003733898657325778</v>
+        <v>0.0003409012788988051</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0006320505695121756</v>
+        <v>0.0005942783477186428</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003299301359931947</v>
+        <v>0.0003165605968453348</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005454849657869337</v>
+        <v>0.0005239904405996528</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003358784149460921</v>
+        <v>0.0003192580363213021</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.000342485032487991</v>
+        <v>0.0003234889106815036</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004933214673267944</v>
+        <v>0.0004784516256870378</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003796645983145623</v>
+        <v>0.0003454349455035921</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003961672861714298</v>
+        <v>0.0003532098084338321</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002869087069048121</v>
+        <v>0.0002850443212163396</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003481737698612061</v>
+        <v>0.0003447852511444076</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002915464175978897</v>
+        <v>0.0002877021666076213</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003460250949422048</v>
+        <v>0.0003434364475200686</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0002939162863575364</v>
+        <v>0.0002890654072850261</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000294240615056969</v>
+        <v>0.0002895923501925809</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0002927663214435026</v>
+        <v>0.0002882773316760242</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0002927282919143347</v>
+        <v>0.0002883449313183616</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0002961782450485968</v>
+        <v>0.0002906344944355603</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0002970444184705509</v>
+        <v>0.0002911712082671522</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003001193539942349</v>
+        <v>0.0002931446077351142</v>
       </c>
       <c r="M33" t="n">
-        <v>0.000293565321389135</v>
+        <v>0.0002888573663097002</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0002953322657938978</v>
+        <v>0.0002899279231284399</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000634387704735155</v>
+        <v>0.0006267379735054339</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0002969191449608646</v>
+        <v>0.0002912656037279991</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0002904655055030655</v>
+        <v>0.0002871308261254868</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003025603335667036</v>
+        <v>0.0002939939762087038</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0002974749277522216</v>
+        <v>0.0002915858150167504</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0002944029628929047</v>
+        <v>0.0002893204903822539</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0004605109907625557</v>
+        <v>0.000455305128199657</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002974388711304618</v>
+        <v>0.0002915586286741867</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004392669892691331</v>
+        <v>0.0004294421263731542</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003425395569640282</v>
+        <v>0.0003183698183195785</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.000319037376446778</v>
+        <v>0.0003039608705688637</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004482633452444877</v>
+        <v>0.0004434837423850274</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.000314983580702102</v>
+        <v>0.000301602969832534</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0002886027070094645</v>
+        <v>0.0002858729865779709</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0003456481389817783</v>
+        <v>0.0003250373430968297</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003855756375946583</v>
+        <v>0.0003788190617177818</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003443108043561427</v>
+        <v>0.0003226483866158826</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003690658744108404</v>
+        <v>0.0003597970657564666</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003205491570217804</v>
+        <v>0.0003087807390692323</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003495143410149773</v>
+        <v>0.0003270918672439497</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003199273439766104</v>
+        <v>0.000308205170109052</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003383948973902986</v>
+        <v>0.0003190807870294939</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003523377048537317</v>
+        <v>0.0003281386337620065</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003909582284937003</v>
+        <v>0.0003514869210991585</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003528891459908903</v>
+        <v>0.0003284368658984101</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0004753318184200879</v>
+        <v>0.0003986157479229557</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003527666420215444</v>
+        <v>0.0003279889796586202</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006855261659978046</v>
+        <v>0.0006678909642682074</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003476148855157116</v>
+        <v>0.0003260095599480798</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003237638621589682</v>
+        <v>0.0003108749887159577</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003209686973781164</v>
+        <v>0.0003088991398983991</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003486342880733714</v>
+        <v>0.0003265173010309498</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003477109819982804</v>
+        <v>0.0003246401016611774</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005950642889353527</v>
+        <v>0.0005639779354392528</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003138471606548216</v>
+        <v>0.0003055696801594991</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005386151208845526</v>
+        <v>0.0005130553113278047</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003386482655046235</v>
+        <v>0.0003195393398022161</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003341467908853959</v>
+        <v>0.0003172703516565113</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004784690148898323</v>
+        <v>0.0004667312972025117</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003568697344921059</v>
+        <v>0.0003306943968964172</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003883515276914845</v>
+        <v>0.0003472899734582418</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0003338719582394094</v>
+        <v>0.0003175548248476939</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003830512323144909</v>
+        <v>0.0003774258507595506</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003528755857831625</v>
+        <v>0.0003276327083831959</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003702354477878388</v>
+        <v>0.0003603687706598969</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003173545639791498</v>
+        <v>0.0003068709708237723</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003453196073023858</v>
+        <v>0.0003246035926544127</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003103012497139871</v>
+        <v>0.0003025410283834327</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003495853110849745</v>
+        <v>0.0003254880635318876</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003485714767239535</v>
+        <v>0.0003258172185166667</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003579786897697033</v>
+        <v>0.0003322213494730891</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003415053884448449</v>
+        <v>0.0003215906489177268</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0004509331933964531</v>
+        <v>0.0003842633123701787</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003317031797200275</v>
+        <v>0.0003154419288919115</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006703178438209709</v>
+        <v>0.0006569134285933604</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003445350505236273</v>
+        <v>0.0003241532964576094</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003178166096041159</v>
+        <v>0.0003073583038868705</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003104292705379675</v>
+        <v>0.0003026992940351193</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003432374738868035</v>
+        <v>0.0003232212947122049</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003389416289207563</v>
+        <v>0.0003193862403381614</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005736001315145007</v>
+        <v>0.0005519887577863601</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003179610568086108</v>
+        <v>0.0003080729928588682</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005319396636129589</v>
+        <v>0.0005099101363809301</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003499864736674819</v>
+        <v>0.0003261262886459511</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003595933766649489</v>
+        <v>0.0003322771291665153</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004765376479643004</v>
+        <v>0.0004657049584757835</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.000357142067395666</v>
+        <v>0.0003306975031865265</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003809680366067196</v>
+        <v>0.0003428695098806148</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0003243596642002141</v>
+        <v>0.0003107273275668022</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003582918143446289</v>
+        <v>0.0003532774562039762</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003287259162094486</v>
+        <v>0.0003125118856639506</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003617979124963488</v>
+        <v>0.000355288931390965</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003175878069130815</v>
+        <v>0.0003057228783081178</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000336061387555275</v>
+        <v>0.0003180165981837484</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003063130654324891</v>
+        <v>0.0002988731961746994</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003427189776621204</v>
+        <v>0.0003203560916957278</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003406583675475661</v>
+        <v>0.0003200707619445191</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003658195242670222</v>
+        <v>0.0003357472168480223</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003319666408458154</v>
+        <v>0.0003149395944613181</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0004183599127908506</v>
+        <v>0.000365245127938466</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003152612244349714</v>
+        <v>0.0003044227033488161</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006649114300615491</v>
+        <v>0.0006519695184930715</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003346609241941852</v>
+        <v>0.0003171896750171328</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003138355767374928</v>
+        <v>0.0003038105820385651</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000315138053723046</v>
+        <v>0.000304047735413243</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003364207804414467</v>
+        <v>0.0003179485244103849</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003382190360111725</v>
+        <v>0.0003176064640353392</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005105058280949877</v>
+        <v>0.0004896107779082111</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003249443370459493</v>
+        <v>0.0003112771130607975</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004593874504415605</v>
+        <v>0.0004453779751763925</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003506836607521569</v>
+        <v>0.0003256221445843903</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003881849347688732</v>
+        <v>0.0003475621420813307</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004685354023530418</v>
+        <v>0.0004595978958661691</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003591782145840081</v>
+        <v>0.0003305085043340011</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00036999520265381</v>
+        <v>0.0003354795719358017</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002992969038669889</v>
+        <v>0.0002942811765909725</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003681415225258158</v>
+        <v>0.0003661181846790051</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003186247436275389</v>
+        <v>0.0003052605022286275</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003569935577150137</v>
+        <v>0.0003505306597929875</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0002985343403941558</v>
+        <v>0.0002934780890822806</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003053620875909638</v>
+        <v>0.0002981690494743202</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003096990779025883</v>
+        <v>0.000299770043070355</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003111512355542789</v>
+        <v>0.0003008007503837216</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003106785825227063</v>
+        <v>0.0003011506360076008</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003314880676441212</v>
+        <v>0.0003136820512199555</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003185872135630724</v>
+        <v>0.0003063154079122555</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0003465322223445315</v>
+        <v>0.0003226041409789574</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003237300769039594</v>
+        <v>0.0003086402405999394</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006343549612325847</v>
+        <v>0.0006285627205701895</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003130166256465386</v>
+        <v>0.0003026351092668027</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003100579115492061</v>
+        <v>0.0003005383404671284</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003075797525162303</v>
+        <v>0.0002986127690190933</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003086418977526382</v>
+        <v>0.0003004240315712062</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003048730842717696</v>
+        <v>0.0002973093008560888</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005403685279938764</v>
+        <v>0.0005273605651663651</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002981589418132924</v>
+        <v>0.0002935715580726908</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005038681187967582</v>
+        <v>0.0004882109301840499</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003184619965456596</v>
+        <v>0.0003052627040151428</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003007384110300958</v>
+        <v>0.0002949181602263469</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004622408409690439</v>
+        <v>0.0004542589958514373</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003223531531914245</v>
+        <v>0.000307746416920375</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003156669586667869</v>
+        <v>0.0003033653819234404</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002929692367925366</v>
+        <v>0.0002899372346089057</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003723109760461602</v>
+        <v>0.0003684582529832759</v>
       </c>
       <c r="D33" t="n">
-        <v>0.000296693465010854</v>
+        <v>0.000292021976918457</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003529076950311247</v>
+        <v>0.0003476445379473672</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0002992792504726882</v>
+        <v>0.0002935099844512723</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000298442193816204</v>
+        <v>0.0002934492311277436</v>
       </c>
       <c r="H33" t="n">
-        <v>0.000299335398460803</v>
+        <v>0.0002933586459721999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.000299405133190048</v>
+        <v>0.0002935420627964883</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003000228547738808</v>
+        <v>0.0002942587118798614</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000295891700353227</v>
+        <v>0.0002916144045642222</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0002979985680793521</v>
+        <v>0.0002932004629376468</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0002935000459065216</v>
+        <v>0.0002901154927578764</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003025460571774668</v>
+        <v>0.0002956081227560192</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006343168831567365</v>
+        <v>0.000627591892066447</v>
       </c>
       <c r="P33" t="n">
-        <v>0.000299659647952035</v>
+        <v>0.0002940668930134905</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0002930570829589302</v>
+        <v>0.0002899636928744117</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003066324932141695</v>
+        <v>0.0002976991971472298</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0002992659296471584</v>
+        <v>0.0002940060250485442</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0002941333692213373</v>
+        <v>0.0002904790865714841</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005151451976977263</v>
+        <v>0.0005123606919148182</v>
       </c>
       <c r="V33" t="n">
-        <v>0.000300281773624854</v>
+        <v>0.0002945202322702294</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004947253031280907</v>
+        <v>0.0004834259645606028</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003419722502470681</v>
+        <v>0.0003193710093580973</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003029877544061985</v>
+        <v>0.0002957681350056433</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004577786009120684</v>
+        <v>0.0004509030864896944</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003099992697856751</v>
+        <v>0.0002999467143299055</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0002900098451290672</v>
+        <v>0.0002879837919671977</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002929587433278706</v>
+        <v>0.0002886715955770814</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003490206681842537</v>
+        <v>0.0003451839532739953</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002938562007684232</v>
+        <v>0.0002889763211272214</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003559541323205113</v>
+        <v>0.0003495595313726442</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0002941799188667256</v>
+        <v>0.000289096798181588</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002915882091008666</v>
+        <v>0.0002878502792738987</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0002915040119302119</v>
+        <v>0.0002874542589348996</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0002915934029764576</v>
+        <v>0.0002875767391553015</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0002949307584820286</v>
+        <v>0.0002898032097918586</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0002903438838458794</v>
+        <v>0.0002869176595070255</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0002956467747603003</v>
+        <v>0.0002904028045886626</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0002896738781842504</v>
+        <v>0.0002864623317867098</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0002943114470825489</v>
+        <v>0.0002892973701993136</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000643712059498555</v>
+        <v>0.0006330150375341915</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0002995231194762721</v>
+        <v>0.0002927978065328875</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0002888021493602816</v>
+        <v>0.0002860369332796144</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003042676423946947</v>
+        <v>0.0002949019696426172</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00029417549049091</v>
+        <v>0.0002894602621755547</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0002894887287091355</v>
+        <v>0.000286362634129146</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0004536122955578983</v>
+        <v>0.000450633648768961</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002983258660977863</v>
+        <v>0.0002920082329591605</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004369597189990712</v>
+        <v>0.0004277877716843833</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003508413811019626</v>
+        <v>0.0003236415523779268</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.000298456461273679</v>
+        <v>0.0002917069106910821</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004493943709769092</v>
+        <v>0.000444145020079656</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003084009911297836</v>
+        <v>0.0002976419178320644</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0002891953810810009</v>
+        <v>0.000286127202315158</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0003256684673227828</v>
+        <v>0.0003122799622751235</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003773129455045868</v>
+        <v>0.0003733024706664917</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003334861539548791</v>
+        <v>0.0003157589355904674</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003636714538983134</v>
+        <v>0.0003561031184556915</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003130059258761665</v>
+        <v>0.0003038537285826751</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000344879570543781</v>
+        <v>0.0003242103880846718</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0003175395131002139</v>
+        <v>0.0003062424777936508</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003379560553835085</v>
+        <v>0.0003183480861884261</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003438997972469562</v>
+        <v>0.0003230258521415942</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003598092998655869</v>
+        <v>0.0003327673915636716</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003450184920863238</v>
+        <v>0.0003235849261494042</v>
       </c>
       <c r="M33" t="n">
-        <v>0.000462427272394788</v>
+        <v>0.0003937124412046516</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003618714223605421</v>
+        <v>0.0003327900235002805</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006659363845791642</v>
+        <v>0.0006533120017423614</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003386843644355505</v>
+        <v>0.0003200355500503206</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003197376304071493</v>
+        <v>0.000308066276779938</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003222074868422491</v>
+        <v>0.0003090157639045394</v>
       </c>
       <c r="S33" t="n">
-        <v>0.000330365305115954</v>
+        <v>0.0003153962666671198</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003343031328824634</v>
+        <v>0.0003162515729298045</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005741909977861605</v>
+        <v>0.0005498772484725788</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003095720000918901</v>
+        <v>0.000302399619097826</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005104778315277105</v>
+        <v>0.0004944461637486162</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003466803375189422</v>
+        <v>0.0003236787662835655</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003289151278775834</v>
+        <v>0.0003136071050474568</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004759789305367043</v>
+        <v>0.0004646798573955713</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003486720681281583</v>
+        <v>0.0003252713797771723</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003743085104383641</v>
+        <v>0.0003387278192378253</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002929310570523038</v>
+        <v>0.0002907860580696981</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0003746231093061776</v>
+        <v>0.0003707831744127567</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003008412137693176</v>
+        <v>0.0002953356920109703</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0003537106291973544</v>
+        <v>0.0003488999113811969</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0002984938517169933</v>
+        <v>0.0002939374006137789</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003348182440266162</v>
+        <v>0.0003170490641112397</v>
       </c>
       <c r="H33" t="n">
-        <v>0.000301543379555333</v>
+        <v>0.0002955426804983621</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0003006907961558097</v>
+        <v>0.0002951703921165116</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0003147936366153393</v>
+        <v>0.0003042200794743268</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003079373442288858</v>
+        <v>0.0002998912783651981</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0003183994875292913</v>
+        <v>0.0003064671563084966</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0003092841686693075</v>
+        <v>0.0003005067075107138</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0003071707416403078</v>
+        <v>0.0002990898888644222</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0006333265685713462</v>
+        <v>0.0006283345445053009</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0003214759241643884</v>
+        <v>0.0003083459211658484</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003043813035428861</v>
+        <v>0.0002977217535192353</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0003100723106351608</v>
+        <v>0.0003005415805227725</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003054954160357647</v>
+        <v>0.0002986205645077416</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0003006029874822044</v>
+        <v>0.0002951576592782453</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0005262905845127911</v>
+        <v>0.0005204651267543727</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0003008125567334908</v>
+        <v>0.000295664486789985</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0005029955556366928</v>
+        <v>0.0004894500061881672</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0003428557420036757</v>
+        <v>0.0003203639553151266</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003460730676683759</v>
+        <v>0.0003223923892247723</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004539461415198673</v>
+        <v>0.0004487846654486457</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0003096427013259115</v>
+        <v>0.0003006374560560878</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003435072768436436</v>
+        <v>0.0003198572463309171</v>
       </c>
     </row>
   </sheetData>
